--- a/2_Teaching_Effectiveness/2b_Student_Course_Evaluations/Z_Misc/Course Evaluation Numbers.xlsx
+++ b/2_Teaching_Effectiveness/2b_Student_Course_Evaluations/Z_Misc/Course Evaluation Numbers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcham\Documents\GitHub\Chamberlain_Tenure_Packet\2_Teaching_Effectiveness\2b_Student_Course_Evaluations\Z_Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7210B9AB-BFF3-4534-8A8C-947F163FE8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7C5ADA-6A4D-4325-9ABD-53B2DEA15D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="435" windowWidth="15885" windowHeight="20685" xr2:uid="{2882075C-5BCF-BB48-99E2-FB2C0697CBA8}"/>
+    <workbookView xWindow="1305" yWindow="2430" windowWidth="16755" windowHeight="17655" xr2:uid="{2882075C-5BCF-BB48-99E2-FB2C0697CBA8}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="25">
   <si>
     <t>Term</t>
   </si>
@@ -232,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -243,24 +243,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -636,7 +629,7 @@
       <c r="E2" s="3">
         <v>12</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="3">
         <v>4.4800000000000004</v>
       </c>
       <c r="G2" s="3">
@@ -645,13 +638,13 @@
       <c r="H2" s="4">
         <v>4.53</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="2">
         <v>3</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="21">
+      <c r="K2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -659,50 +652,50 @@
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>2021</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="17"/>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>2021</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>10</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>9</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4">
         <v>4.8099999999999996</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I4" s="5">
         <v>4</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" s="6">
@@ -713,31 +706,31 @@
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>2021</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>25</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5">
         <v>19</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5">
         <v>4.59</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="5">
         <v>6</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" s="6">
@@ -748,22 +741,22 @@
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>2022</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6">
         <v>29</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6">
         <v>16</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6">
         <v>4.43</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <v>4.5199999999999996</v>
       </c>
       <c r="H6" s="6">
@@ -772,7 +765,7 @@
       <c r="I6" s="5">
         <v>2</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" s="6">
@@ -783,22 +776,22 @@
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>2022</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7">
         <v>32</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7">
         <v>20</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7">
         <v>4.6100000000000003</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <v>4.5199999999999996</v>
       </c>
       <c r="H7" s="6">
@@ -807,7 +800,7 @@
       <c r="I7" s="5">
         <v>6</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" s="6">
@@ -815,49 +808,49 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8">
         <v>2022</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="7">
         <v>2022</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="15"/>
+      <c r="C9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="3">
-        <f>B2+1</f>
+        <f t="shared" ref="B10:B41" si="0">B2+1</f>
         <v>2022</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -869,7 +862,7 @@
       <c r="E10" s="3">
         <v>25</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="3">
         <v>4.67</v>
       </c>
       <c r="G10" s="3">
@@ -878,7 +871,7 @@
       <c r="H10" s="4">
         <v>4.49</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="3">
         <v>8</v>
       </c>
       <c r="J10" s="3">
@@ -892,52 +885,52 @@
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="8">
-        <f>B3+1</f>
+      <c r="B11">
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17"/>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="8">
-        <f>B4+1</f>
+      <c r="B12">
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12">
         <v>20</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12">
         <v>14</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12">
         <v>4.91</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12">
         <v>4.75</v>
       </c>
       <c r="H12" s="6">
         <v>4.5599999999999996</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="6">
@@ -948,52 +941,52 @@
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="8">
-        <f>B5+1</f>
+      <c r="B13">
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="8">
-        <f>B6+1</f>
+      <c r="B14">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14">
         <v>34</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14">
         <v>19</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14">
         <v>4.6100000000000003</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14">
         <v>4.46</v>
       </c>
       <c r="H14" s="6">
         <v>4.49</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14">
         <v>5</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" s="6">
@@ -1004,52 +997,52 @@
       <c r="A15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="8">
-        <f>B7+1</f>
+      <c r="B15">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="17"/>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="8">
-        <f>B8+1</f>
+      <c r="B16">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16">
         <v>35</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16">
         <v>21</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16">
         <v>4.75</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16">
         <v>4.46</v>
       </c>
       <c r="H16" s="6">
         <v>4.49</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16">
         <v>7</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" s="6">
@@ -1057,43 +1050,43 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="7">
-        <f>B9+1</f>
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="15"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="3">
-        <f>B10+1</f>
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="3">
         <v>24</v>
       </c>
       <c r="E18" s="3">
         <v>16</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="3">
         <v>4.84</v>
       </c>
       <c r="G18" s="3">
@@ -1102,7 +1095,7 @@
       <c r="H18" s="4">
         <v>4.5199999999999996</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="3">
         <v>7</v>
       </c>
       <c r="J18" s="3">
@@ -1116,52 +1109,52 @@
       <c r="A19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="8">
-        <f>B11+1</f>
+      <c r="B19">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17"/>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="8">
-        <f>B12+1</f>
+      <c r="B20">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20">
         <v>29</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20">
         <v>14</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20">
         <v>4.63</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20">
         <v>4.43</v>
       </c>
       <c r="H20" s="6">
         <v>4.47</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20">
         <v>4</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" s="6">
@@ -1172,52 +1165,52 @@
       <c r="A21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="8">
-        <f>B13+1</f>
+      <c r="B21">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="17"/>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="8">
-        <f>B14+1</f>
+      <c r="B22">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22">
         <v>4</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22">
         <v>4</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22">
         <v>4.72</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22">
         <v>4.53</v>
       </c>
       <c r="H22" s="6">
         <v>4.53</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22">
         <v>2</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" s="6">
@@ -1228,80 +1221,80 @@
       <c r="A23" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="8">
-        <f>B15+1</f>
+      <c r="B23">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="17"/>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="8">
-        <f>B16+1</f>
+      <c r="B24">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="17"/>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="7">
-        <f>B17+1</f>
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="15"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="10"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="3">
-        <f>B18+1</f>
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="3">
         <v>6</v>
       </c>
       <c r="E26" s="3">
         <v>3</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="3">
         <v>4.1500000000000004</v>
       </c>
       <c r="G26" s="3">
@@ -1310,7 +1303,7 @@
       <c r="H26" s="4">
         <v>4.5599999999999996</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="3">
         <v>2</v>
       </c>
       <c r="J26" s="3">
@@ -1324,32 +1317,32 @@
       <c r="A27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="8">
-        <f>B19+1</f>
+      <c r="B27">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27">
         <v>17</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27">
         <v>8</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27">
         <v>4.78</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27">
         <v>4.5599999999999996</v>
       </c>
       <c r="H27" s="6">
         <v>4.5599999999999996</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27">
         <v>5</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27">
         <v>1</v>
       </c>
       <c r="K27" s="6">
@@ -1360,72 +1353,72 @@
       <c r="A28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="8">
-        <f>B20+1</f>
+      <c r="B28">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="17"/>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="8">
-        <f>B21+1</f>
+      <c r="B29">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="17"/>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="8">
-        <f>B22+1</f>
+      <c r="B30">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30">
         <v>20</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30">
         <v>16</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30">
         <v>4.62</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30">
         <v>4.55</v>
       </c>
       <c r="H30" s="6">
         <v>4.55</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30">
         <v>5</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" s="6">
@@ -1436,80 +1429,80 @@
       <c r="A31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="8">
-        <f>B23+1</f>
+      <c r="B31">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="17"/>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="8">
-        <f>B24+1</f>
+      <c r="B32">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="17"/>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B33" s="7">
-        <f>B25+1</f>
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="10"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="3">
-        <f>B26+1</f>
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="3">
         <v>15</v>
       </c>
       <c r="E34" s="3">
         <v>8</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="3">
         <v>4.74</v>
       </c>
       <c r="G34" s="3">
@@ -1518,7 +1511,7 @@
       <c r="H34" s="4">
         <v>4.67</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="3">
         <v>1</v>
       </c>
       <c r="J34" s="3">
@@ -1532,32 +1525,32 @@
       <c r="A35" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="8">
-        <f>B27+1</f>
+      <c r="B35">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="10">
-        <v>11</v>
-      </c>
-      <c r="E35" s="8">
+      <c r="D35">
+        <v>11</v>
+      </c>
+      <c r="E35">
         <v>8</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35">
         <v>4.45</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35">
         <v>4.67</v>
       </c>
       <c r="H35" s="6">
         <v>4.67</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35">
         <v>5</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35">
         <v>2</v>
       </c>
       <c r="K35" s="6">
@@ -1568,32 +1561,32 @@
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="8">
-        <f>B28+1</f>
+      <c r="B36">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36">
         <v>10</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36">
         <v>5</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36">
         <v>4.8</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36">
         <v>4.67</v>
       </c>
       <c r="H36" s="6">
         <v>4.68</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36">
         <v>5</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" s="6">
@@ -1604,128 +1597,134 @@
       <c r="A37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="8">
-        <f>B29+1</f>
+      <c r="B37">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37">
         <v>15</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37">
         <v>8</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37">
         <v>4.75</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37">
         <v>4.67</v>
       </c>
       <c r="H37" s="6">
         <v>4.66</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="6"/>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="8">
-        <f>B30+1</f>
+      <c r="B38">
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="D38">
+        <v>9</v>
+      </c>
       <c r="H38" s="6"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
       <c r="K38" s="6"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="8">
-        <f>B31+1</f>
+      <c r="B39">
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="D39">
+        <v>25</v>
+      </c>
       <c r="H39" s="6"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
       <c r="K39" s="6"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="8">
-        <f>B32+1</f>
+      <c r="B40">
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="17"/>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="12"/>
     </row>
     <row r="41" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B41" s="7">
-        <f>B33+1</f>
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="15"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D42">
         <f>SUM(D2:D41)</f>
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="E42">
         <f>SUM(E2:E41)</f>
         <v>245</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="17">
         <f>SUMPRODUCT(E2:E41,F2:F41)/E42</f>
         <v>4.6589387755102036</v>
       </c>
+      <c r="G42" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>24</v>
+      </c>
       <c r="I42">
         <f>SUM(I2:I41)</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J42">
         <f>SUM(J2:J41)</f>

--- a/2_Teaching_Effectiveness/2b_Student_Course_Evaluations/Z_Misc/Course Evaluation Numbers.xlsx
+++ b/2_Teaching_Effectiveness/2b_Student_Course_Evaluations/Z_Misc/Course Evaluation Numbers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcham\Documents\GitHub\Chamberlain_Tenure_Packet\2_Teaching_Effectiveness\2b_Student_Course_Evaluations\Z_Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7C5ADA-6A4D-4325-9ABD-53B2DEA15D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A26EF7E-591A-4ABB-831C-E9A1C4041565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="2430" windowWidth="16755" windowHeight="17655" xr2:uid="{2882075C-5BCF-BB48-99E2-FB2C0697CBA8}"/>
+    <workbookView xWindow="8475" yWindow="1920" windowWidth="17505" windowHeight="17655" xr2:uid="{2882075C-5BCF-BB48-99E2-FB2C0697CBA8}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -232,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -257,6 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1643,8 +1644,27 @@
       <c r="D38">
         <v>9</v>
       </c>
-      <c r="H38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="E38">
+        <v>6</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H38" s="6">
+        <v>4.62</v>
+      </c>
+      <c r="I38" s="18">
+        <v>3</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -1660,8 +1680,27 @@
       <c r="D39">
         <v>25</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="E39">
+        <v>17</v>
+      </c>
+      <c r="F39">
+        <v>4.71</v>
+      </c>
+      <c r="G39">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H39" s="6">
+        <v>4.62</v>
+      </c>
+      <c r="I39" s="18">
+        <v>1</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
@@ -1710,11 +1749,11 @@
       </c>
       <c r="E42">
         <f>SUM(E2:E41)</f>
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F42" s="17">
         <f>SUMPRODUCT(E2:E41,F2:F41)/E42</f>
-        <v>4.6589387755102036</v>
+        <v>4.6698134328358201</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>24</v>
@@ -1724,7 +1763,7 @@
       </c>
       <c r="I42">
         <f>SUM(I2:I41)</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J42">
         <f>SUM(J2:J41)</f>
